--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260814.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,330,658</t>
+          <t>115,584,242</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>17,801,722</t>
+          <t>1,330,658</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>261,874,216</t>
+          <t>17,801,722</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>115,584,242</t>
+          <t>261,874,216</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
